--- a/outputs/analysis/email_campaign_performance.xlsx
+++ b/outputs/analysis/email_campaign_performance.xlsx
@@ -788,7 +788,7 @@
     <t>Event-type rows divided by all engagement-event rows in the same group.</t>
   </si>
   <si>
-    <t>Distinct prospect IDs with at least one recorded engagement.</t>
+    <t>Distinct supplied prospect IDs; valid normalized email fallback only when ID is missing.</t>
   </si>
   <si>
     <t>Observed activity mix among recorded engagements.</t>
@@ -1178,7 +1178,7 @@
         <v>1264</v>
       </c>
       <c r="C2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D2">
         <v>1165</v>
@@ -1254,7 +1254,7 @@
         <v>1300</v>
       </c>
       <c r="C4">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="D4">
         <v>1252</v>
@@ -1292,7 +1292,7 @@
         <v>1451</v>
       </c>
       <c r="C5">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="D5">
         <v>1408</v>
@@ -1330,7 +1330,7 @@
         <v>797</v>
       </c>
       <c r="C6">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D6">
         <v>760</v>
@@ -1368,7 +1368,7 @@
         <v>1166</v>
       </c>
       <c r="C7">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D7">
         <v>1134</v>
@@ -1406,7 +1406,7 @@
         <v>819</v>
       </c>
       <c r="C8">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D8">
         <v>789</v>
@@ -1444,7 +1444,7 @@
         <v>846</v>
       </c>
       <c r="C9">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D9">
         <v>827</v>
@@ -1482,7 +1482,7 @@
         <v>354</v>
       </c>
       <c r="C10">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D10">
         <v>335</v>
@@ -1520,7 +1520,7 @@
         <v>245</v>
       </c>
       <c r="C11">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D11">
         <v>228</v>
@@ -1558,7 +1558,7 @@
         <v>1008</v>
       </c>
       <c r="C12">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="D12">
         <v>993</v>
@@ -1596,7 +1596,7 @@
         <v>359</v>
       </c>
       <c r="C13">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D13">
         <v>344</v>
@@ -1634,7 +1634,7 @@
         <v>122</v>
       </c>
       <c r="C14">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D14">
         <v>108</v>
@@ -1748,7 +1748,7 @@
         <v>599</v>
       </c>
       <c r="C17">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D17">
         <v>587</v>
@@ -1786,7 +1786,7 @@
         <v>557</v>
       </c>
       <c r="C18">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D18">
         <v>545</v>
@@ -2014,7 +2014,7 @@
         <v>208</v>
       </c>
       <c r="C24">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D24">
         <v>199</v>
@@ -2584,7 +2584,7 @@
         <v>344</v>
       </c>
       <c r="C39">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D39">
         <v>338</v>
@@ -2622,7 +2622,7 @@
         <v>296</v>
       </c>
       <c r="C40">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D40">
         <v>290</v>
@@ -2774,7 +2774,7 @@
         <v>303</v>
       </c>
       <c r="C44">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D44">
         <v>298</v>
@@ -2812,7 +2812,7 @@
         <v>289</v>
       </c>
       <c r="C45">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D45">
         <v>284</v>
@@ -2850,7 +2850,7 @@
         <v>94</v>
       </c>
       <c r="C46">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D46">
         <v>89</v>
@@ -2926,7 +2926,7 @@
         <v>58</v>
       </c>
       <c r="C48">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D48">
         <v>54</v>
@@ -3496,7 +3496,7 @@
         <v>11</v>
       </c>
       <c r="C63">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D63">
         <v>10</v>
@@ -4060,7 +4060,7 @@
         <v>6</v>
       </c>
       <c r="C78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D78">
         <v>6</v>
@@ -5207,7 +5207,7 @@
         <v>2285</v>
       </c>
       <c r="C2">
-        <v>614</v>
+        <v>633</v>
       </c>
       <c r="D2">
         <v>2062</v>
@@ -5497,7 +5497,7 @@
         <v>7070</v>
       </c>
       <c r="C2">
-        <v>2100</v>
+        <v>2119</v>
       </c>
       <c r="D2">
         <v>6776</v>
@@ -6242,7 +6242,7 @@
         <v>3786</v>
       </c>
       <c r="C2">
-        <v>2076</v>
+        <v>2080</v>
       </c>
       <c r="D2">
         <v>3524</v>
@@ -6277,7 +6277,7 @@
         <v>7583</v>
       </c>
       <c r="C3">
-        <v>3383</v>
+        <v>3394</v>
       </c>
       <c r="D3">
         <v>7341</v>
@@ -6312,7 +6312,7 @@
         <v>3645</v>
       </c>
       <c r="C4">
-        <v>2556</v>
+        <v>2566</v>
       </c>
       <c r="D4">
         <v>3451</v>
@@ -6347,7 +6347,7 @@
         <v>2116</v>
       </c>
       <c r="C5">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D5">
         <v>1901</v>
